--- a/Bibsam_tidskriftslistor/scifree_data_iop.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_iop.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="17" documentId="11_7A01F9B85FC45E18C16D0A9E96CF08FD57B1F690" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA8BA79A-D657-445B-BB86-3852CC73EDEE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1A3DD60-BDDF-45A2-90CC-C0866933A82A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="285">
   <si>
     <t>ISSN Electronic</t>
   </si>
@@ -757,9 +757,6 @@
     <t>International Journal of Extreme Manufacturing</t>
   </si>
   <si>
-    <t>Materials Futures</t>
-  </si>
-  <si>
     <t>Neuromorphic Computing and Engineering</t>
   </si>
   <si>
@@ -784,9 +781,6 @@
     <t>2631-7990</t>
   </si>
   <si>
-    <t>2752-5724</t>
-  </si>
-  <si>
     <t>2634-4386</t>
   </si>
   <si>
@@ -811,9 +805,6 @@
     <t>https://iopscience.iop.org/journal/2752-5309</t>
   </si>
   <si>
-    <t>https://iopscience.iop.org/journal/2752-5724</t>
-  </si>
-  <si>
     <t>https://iopscience.iop.org/journal/2752-664X</t>
   </si>
   <si>
@@ -872,6 +863,18 @@
   </si>
   <si>
     <t>Quantum Science &amp; Technology</t>
+  </si>
+  <si>
+    <t>1350-4533</t>
+  </si>
+  <si>
+    <t>1873-4030</t>
+  </si>
+  <si>
+    <t>Medical Engineering &amp; Physics</t>
+  </si>
+  <si>
+    <t>https://iopscience.iop.org/journal/1873-4030</t>
   </si>
 </sst>
 </file>
@@ -927,16 +930,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{10EDBF25-75CA-4FB7-A14A-6BF4B564DEF6}" name="Table2" displayName="Table2" ref="A1:G80" totalsRowShown="0">
-  <autoFilter ref="A1:G80" xr:uid="{10EDBF25-75CA-4FB7-A14A-6BF4B564DEF6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00A77A78-5A5E-426A-A698-89B572CA1D4B}" name="Table1" displayName="Table1" ref="A1:G80" totalsRowShown="0">
+  <autoFilter ref="A1:G80" xr:uid="{00A77A78-5A5E-426A-A698-89B572CA1D4B}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{25451636-62A7-49CC-9A8A-006B2E4DCB19}" name="Imprint"/>
-    <tableColumn id="2" xr3:uid="{90E81C64-733B-4D81-BCAE-E916703CB523}" name="ISSN Electronic"/>
-    <tableColumn id="3" xr3:uid="{34C9838C-DB7C-44C2-8A73-961AB6D89028}" name="ISSN Print"/>
-    <tableColumn id="4" xr3:uid="{5FDFFA4B-3F55-44AB-AA64-5E38911592F1}" name="Journal Name"/>
-    <tableColumn id="5" xr3:uid="{2894B0D8-C1AA-42ED-BFDD-B75E8D384292}" name="JournalURL"/>
-    <tableColumn id="6" xr3:uid="{170E927E-ADF4-429A-8F67-CC8C2C63F0DB}" name="Publishing model"/>
-    <tableColumn id="7" xr3:uid="{05620A47-B727-463A-BAF1-42B35F624FB7}" name="CC License options"/>
+    <tableColumn id="1" xr3:uid="{2669FACA-8449-4D57-AB24-912C699CA10F}" name="Imprint"/>
+    <tableColumn id="2" xr3:uid="{1CA3D1CE-0538-4292-B194-D7236A258A7B}" name="ISSN Electronic"/>
+    <tableColumn id="3" xr3:uid="{4C5FD8DC-D8FB-4D18-81D0-82F467D1F29F}" name="ISSN Print"/>
+    <tableColumn id="4" xr3:uid="{0C0FFF98-B7E4-4D82-8297-33297544A450}" name="Journal Name"/>
+    <tableColumn id="5" xr3:uid="{D03A521C-2124-4596-B9D1-F1922CC2C285}" name="JournalURL"/>
+    <tableColumn id="6" xr3:uid="{84DC6E97-DC1E-4529-B7FB-47D76D71BCB2}" name="Publishing model"/>
+    <tableColumn id="7" xr3:uid="{71382CEC-A432-4EAA-9018-10EFF604BC66}" name="CC License options"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1204,14 +1207,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6192A3F6-8973-4FF0-A4E6-7EA3789B1E59}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C5C2CF9-F451-48AC-9CCA-53B8DD7C7289}">
   <dimension ref="A1:G80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
     <col min="2" max="2" width="16.28515625" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" customWidth="1"/>
+    <col min="4" max="4" width="31.85546875" customWidth="1"/>
     <col min="5" max="5" width="12.85546875" customWidth="1"/>
     <col min="6" max="6" width="18.5703125" customWidth="1"/>
     <col min="7" max="7" width="19.5703125" customWidth="1"/>
@@ -1265,13 +1268,13 @@
         <v>172</v>
       </c>
       <c r="B3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D3" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="E3" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F3" t="s">
         <v>7</v>
@@ -1334,7 +1337,7 @@
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E6" t="s">
         <v>126</v>
@@ -1417,13 +1420,13 @@
         <v>172</v>
       </c>
       <c r="B10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D10" t="s">
         <v>238</v>
       </c>
       <c r="E10" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F10" t="s">
         <v>209</v>
@@ -1437,16 +1440,16 @@
         <v>172</v>
       </c>
       <c r="B11" t="s">
+        <v>268</v>
+      </c>
+      <c r="C11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D11" t="s">
+        <v>270</v>
+      </c>
+      <c r="E11" t="s">
         <v>271</v>
-      </c>
-      <c r="C11" t="s">
-        <v>272</v>
-      </c>
-      <c r="D11" t="s">
-        <v>273</v>
-      </c>
-      <c r="E11" t="s">
-        <v>274</v>
       </c>
       <c r="F11" t="s">
         <v>7</v>
@@ -1460,13 +1463,13 @@
         <v>172</v>
       </c>
       <c r="B12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D12" t="s">
         <v>239</v>
       </c>
       <c r="E12" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F12" t="s">
         <v>209</v>
@@ -1560,13 +1563,13 @@
         <v>172</v>
       </c>
       <c r="B17" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D17" t="s">
         <v>240</v>
       </c>
       <c r="E17" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F17" t="s">
         <v>209</v>
@@ -1580,13 +1583,13 @@
         <v>172</v>
       </c>
       <c r="B18" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D18" t="s">
         <v>241</v>
       </c>
       <c r="E18" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F18" t="s">
         <v>209</v>
@@ -1600,13 +1603,13 @@
         <v>172</v>
       </c>
       <c r="B19" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D19" t="s">
         <v>242</v>
       </c>
       <c r="E19" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F19" t="s">
         <v>209</v>
@@ -1620,13 +1623,13 @@
         <v>172</v>
       </c>
       <c r="B20" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D20" t="s">
         <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F20" t="s">
         <v>209</v>
@@ -1646,7 +1649,7 @@
         <v>234</v>
       </c>
       <c r="E21" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F21" t="s">
         <v>7</v>
@@ -1746,13 +1749,13 @@
         <v>172</v>
       </c>
       <c r="B26" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D26" t="s">
         <v>244</v>
       </c>
       <c r="E26" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F26" t="s">
         <v>209</v>
@@ -1772,7 +1775,7 @@
         <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E27" t="s">
         <v>133</v>
@@ -2036,7 +2039,7 @@
         <v>45</v>
       </c>
       <c r="D39" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E39" t="s">
         <v>146</v>
@@ -2199,16 +2202,16 @@
         <v>172</v>
       </c>
       <c r="B47" t="s">
+        <v>274</v>
+      </c>
+      <c r="C47" t="s">
+        <v>275</v>
+      </c>
+      <c r="D47" t="s">
+        <v>276</v>
+      </c>
+      <c r="E47" t="s">
         <v>277</v>
-      </c>
-      <c r="C47" t="s">
-        <v>278</v>
-      </c>
-      <c r="D47" t="s">
-        <v>279</v>
-      </c>
-      <c r="E47" t="s">
-        <v>280</v>
       </c>
       <c r="F47" t="s">
         <v>7</v>
@@ -2308,13 +2311,13 @@
         <v>172</v>
       </c>
       <c r="B52" t="s">
-        <v>254</v>
+        <v>188</v>
       </c>
       <c r="D52" t="s">
-        <v>245</v>
+        <v>177</v>
       </c>
       <c r="E52" t="s">
-        <v>263</v>
+        <v>199</v>
       </c>
       <c r="F52" t="s">
         <v>209</v>
@@ -2328,16 +2331,19 @@
         <v>172</v>
       </c>
       <c r="B53" t="s">
-        <v>188</v>
+        <v>53</v>
+      </c>
+      <c r="C53" t="s">
+        <v>54</v>
       </c>
       <c r="D53" t="s">
-        <v>177</v>
+        <v>107</v>
       </c>
       <c r="E53" t="s">
-        <v>199</v>
+        <v>152</v>
       </c>
       <c r="F53" t="s">
-        <v>209</v>
+        <v>7</v>
       </c>
       <c r="G53" t="s">
         <v>8</v>
@@ -2348,16 +2354,16 @@
         <v>172</v>
       </c>
       <c r="B54" t="s">
-        <v>53</v>
+        <v>281</v>
       </c>
       <c r="C54" t="s">
-        <v>54</v>
+        <v>282</v>
       </c>
       <c r="D54" t="s">
-        <v>107</v>
+        <v>283</v>
       </c>
       <c r="E54" t="s">
-        <v>152</v>
+        <v>284</v>
       </c>
       <c r="F54" t="s">
         <v>7</v>
@@ -2403,7 +2409,7 @@
         <v>154</v>
       </c>
       <c r="F56" t="s">
-        <v>7</v>
+        <v>209</v>
       </c>
       <c r="G56" t="s">
         <v>8</v>
@@ -2483,7 +2489,7 @@
         <v>62</v>
       </c>
       <c r="D60" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E60" t="s">
         <v>157</v>
@@ -2500,13 +2506,13 @@
         <v>172</v>
       </c>
       <c r="B61" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D61" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E61" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F61" t="s">
         <v>209</v>
@@ -2681,7 +2687,7 @@
         <v>74</v>
       </c>
       <c r="D69" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E69" t="s">
         <v>163</v>
@@ -2807,7 +2813,7 @@
         <v>80</v>
       </c>
       <c r="D75" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E75" t="s">
         <v>167</v>
@@ -2830,7 +2836,7 @@
         <v>235</v>
       </c>
       <c r="E76" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F76" t="s">
         <v>7</v>
